--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/15.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/15.xlsx
@@ -426,13 +426,13 @@
         <v>-22.11041350959481</v>
       </c>
       <c r="E2">
-        <v>-27.39685773197857</v>
+        <v>-30.92863725293072</v>
       </c>
       <c r="F2">
-        <v>-3.048288492507742</v>
+        <v>-4.933267535358982</v>
       </c>
       <c r="G2">
-        <v>-19.46046044725909</v>
+        <v>-18.62567659462201</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-22.12629366021865</v>
       </c>
       <c r="E3">
-        <v>-27.7234195780937</v>
+        <v>-32.33276986730404</v>
       </c>
       <c r="F3">
-        <v>-2.716319977042903</v>
+        <v>-3.735797402282822</v>
       </c>
       <c r="G3">
-        <v>-19.69350298995055</v>
+        <v>-20.51514397679673</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.04175172237303</v>
       </c>
       <c r="E4">
-        <v>-26.79995504455353</v>
+        <v>-33.30866733714203</v>
       </c>
       <c r="F4">
-        <v>-2.744221707861115</v>
+        <v>-4.94624521348305</v>
       </c>
       <c r="G4">
-        <v>-19.50713913936282</v>
+        <v>-19.51093467982359</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-21.83222019664218</v>
       </c>
       <c r="E5">
-        <v>-29.61357292957725</v>
+        <v>-32.28018069865297</v>
       </c>
       <c r="F5">
-        <v>-3.07659090092256</v>
+        <v>-4.129760085807539</v>
       </c>
       <c r="G5">
-        <v>-19.43654341101063</v>
+        <v>-19.03196495120184</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.49119497056268</v>
       </c>
       <c r="E6">
-        <v>-28.52936115418681</v>
+        <v>-31.90232709168996</v>
       </c>
       <c r="F6">
-        <v>-2.909399067429618</v>
+        <v>-4.835346998607361</v>
       </c>
       <c r="G6">
-        <v>-20.28183327991659</v>
+        <v>-19.9265786380974</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-21.01052861873254</v>
       </c>
       <c r="E7">
-        <v>-29.68726252286707</v>
+        <v>-33.38968173713925</v>
       </c>
       <c r="F7">
-        <v>-2.754446905104149</v>
+        <v>-4.479963391182749</v>
       </c>
       <c r="G7">
-        <v>-18.67159220597893</v>
+        <v>-18.11520040410301</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-20.39092157186992</v>
       </c>
       <c r="E8">
-        <v>-29.81577835096775</v>
+        <v>-34.16987441002475</v>
       </c>
       <c r="F8">
-        <v>-2.434061614704834</v>
+        <v>-4.225954383111332</v>
       </c>
       <c r="G8">
-        <v>-18.80884245821881</v>
+        <v>-19.13244828468257</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-19.66610171647748</v>
       </c>
       <c r="E9">
-        <v>-30.45204932717847</v>
+        <v>-33.27857109888705</v>
       </c>
       <c r="F9">
-        <v>-2.75362021061629</v>
+        <v>-4.371218224499099</v>
       </c>
       <c r="G9">
-        <v>-18.13615781263937</v>
+        <v>-19.4720986701024</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-18.86688411197691</v>
       </c>
       <c r="E10">
-        <v>-31.1970172649953</v>
+        <v>-34.69847412399209</v>
       </c>
       <c r="F10">
-        <v>-2.581464250931403</v>
+        <v>-4.273164656450581</v>
       </c>
       <c r="G10">
-        <v>-18.29264564500795</v>
+        <v>-16.58863998976151</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-18.02521446166443</v>
       </c>
       <c r="E11">
-        <v>-32.40917654499847</v>
+        <v>-34.98519898426174</v>
       </c>
       <c r="F11">
-        <v>-2.513942949226642</v>
+        <v>-4.293425006226798</v>
       </c>
       <c r="G11">
-        <v>-17.76265213326218</v>
+        <v>-17.63492466526602</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-17.1693153312044</v>
       </c>
       <c r="E12">
-        <v>-32.52405034515104</v>
+        <v>-35.76553656831549</v>
       </c>
       <c r="F12">
-        <v>-2.028071476605312</v>
+        <v>-4.152660473344794</v>
       </c>
       <c r="G12">
-        <v>-17.21945947645133</v>
+        <v>-17.97068681494998</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.32554658271834</v>
       </c>
       <c r="E13">
-        <v>-33.43870246827228</v>
+        <v>-35.57283188539309</v>
       </c>
       <c r="F13">
-        <v>-2.457757814464597</v>
+        <v>-4.407960993590252</v>
       </c>
       <c r="G13">
-        <v>-16.90279917452896</v>
+        <v>-17.6024846295267</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.54117207882789</v>
       </c>
       <c r="E14">
-        <v>-35.0148061473239</v>
+        <v>-36.33598164635071</v>
       </c>
       <c r="F14">
-        <v>-2.590389225617861</v>
+        <v>-4.427616367706771</v>
       </c>
       <c r="G14">
-        <v>-16.60729160332977</v>
+        <v>-17.88603782078358</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.84066982451377</v>
       </c>
       <c r="E15">
-        <v>-35.30458999178573</v>
+        <v>-36.87791998050765</v>
       </c>
       <c r="F15">
-        <v>-2.148051453053089</v>
+        <v>-4.569230558812409</v>
       </c>
       <c r="G15">
-        <v>-15.12023096309008</v>
+        <v>-16.47503365376311</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.23973905181098</v>
       </c>
       <c r="E16">
-        <v>-34.91690053927806</v>
+        <v>-38.06711763305492</v>
       </c>
       <c r="F16">
-        <v>-1.853344370366709</v>
+        <v>-3.90801591835137</v>
       </c>
       <c r="G16">
-        <v>-14.98124267444209</v>
+        <v>-16.3149555347572</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.73595202179366</v>
       </c>
       <c r="E17">
-        <v>-36.73820297194899</v>
+        <v>-38.87352564197082</v>
       </c>
       <c r="F17">
-        <v>-1.640873592898395</v>
+        <v>-3.679870411584994</v>
       </c>
       <c r="G17">
-        <v>-14.9155316560331</v>
+        <v>-17.07434502328292</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.33172581580946</v>
       </c>
       <c r="E18">
-        <v>-36.44618885403838</v>
+        <v>-38.62819103413127</v>
       </c>
       <c r="F18">
-        <v>-1.763057296127506</v>
+        <v>-3.841592916698966</v>
       </c>
       <c r="G18">
-        <v>-15.5055701874974</v>
+        <v>-15.99785161973256</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.0333876710409</v>
       </c>
       <c r="E19">
-        <v>-38.01770292468322</v>
+        <v>-37.61338717985639</v>
       </c>
       <c r="F19">
-        <v>-1.567245521183699</v>
+        <v>-3.73972578480607</v>
       </c>
       <c r="G19">
-        <v>-14.35251048671478</v>
+        <v>-15.06735327446407</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.82865983583252</v>
       </c>
       <c r="E20">
-        <v>-37.98445939699291</v>
+        <v>-38.53399651053472</v>
       </c>
       <c r="F20">
-        <v>-1.553846577286124</v>
+        <v>-3.636430150177448</v>
       </c>
       <c r="G20">
-        <v>-13.63145877080659</v>
+        <v>-15.22493358686061</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.69925813327041</v>
       </c>
       <c r="E21">
-        <v>-38.35267188279359</v>
+        <v>-41.74628992600872</v>
       </c>
       <c r="F21">
-        <v>-1.661072969996867</v>
+        <v>-3.353107537464203</v>
       </c>
       <c r="G21">
-        <v>-14.98108211298343</v>
+        <v>-14.39580249073183</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.61632976000978</v>
       </c>
       <c r="E22">
-        <v>-38.6347029797543</v>
+        <v>-38.41423648692787</v>
       </c>
       <c r="F22">
-        <v>-1.14051596226854</v>
+        <v>-2.99086965083757</v>
       </c>
       <c r="G22">
-        <v>-13.94711432215779</v>
+        <v>-14.87511320554413</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.56861335429971</v>
       </c>
       <c r="E23">
-        <v>-38.85038740402862</v>
+        <v>-40.69543941863279</v>
       </c>
       <c r="F23">
-        <v>-0.9438228549827916</v>
+        <v>-3.113079485214286</v>
       </c>
       <c r="G23">
-        <v>-13.67697380615326</v>
+        <v>-14.44995308411769</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.54788749883227</v>
       </c>
       <c r="E24">
-        <v>-39.55268579550818</v>
+        <v>-41.19841702666474</v>
       </c>
       <c r="F24">
-        <v>-1.290633070434172</v>
+        <v>-2.76368386985595</v>
       </c>
       <c r="G24">
-        <v>-14.10274968905001</v>
+        <v>-13.81606968753128</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.54067103682668</v>
       </c>
       <c r="E25">
-        <v>-40.1482163553089</v>
+        <v>-40.61617527383953</v>
       </c>
       <c r="F25">
-        <v>-0.9826204824992272</v>
+        <v>-2.875954365907368</v>
       </c>
       <c r="G25">
-        <v>-13.36650753493487</v>
+        <v>-14.63202977823207</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.5334454760155</v>
       </c>
       <c r="E26">
-        <v>-39.49830335115007</v>
+        <v>-42.87964696556741</v>
       </c>
       <c r="F26">
-        <v>-1.047811360949419</v>
+        <v>-3.203294500834336</v>
       </c>
       <c r="G26">
-        <v>-13.41505999581382</v>
+        <v>-15.16226827034775</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.50964002857732</v>
       </c>
       <c r="E27">
-        <v>-41.4966011904108</v>
+        <v>-41.08803094425376</v>
       </c>
       <c r="F27">
-        <v>-1.120103576724441</v>
+        <v>-3.414993221668873</v>
       </c>
       <c r="G27">
-        <v>-13.66071406173713</v>
+        <v>-14.65810860071768</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.47189911739034</v>
       </c>
       <c r="E28">
-        <v>-39.98676040727642</v>
+        <v>-42.85176967957619</v>
       </c>
       <c r="F28">
-        <v>-1.281797575131935</v>
+        <v>-2.83702212338812</v>
       </c>
       <c r="G28">
-        <v>-13.95467229762395</v>
+        <v>-14.60586653683521</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.42092121153036</v>
       </c>
       <c r="E29">
-        <v>-39.72509385792821</v>
+        <v>-40.88711840219246</v>
       </c>
       <c r="F29">
-        <v>-0.9978676112001205</v>
+        <v>-2.684979228829314</v>
       </c>
       <c r="G29">
-        <v>-13.93058476828021</v>
+        <v>-14.15298059651737</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.35526192265485</v>
       </c>
       <c r="E30">
-        <v>-40.00513242632554</v>
+        <v>-40.83336315148441</v>
       </c>
       <c r="F30">
-        <v>-1.263624549752268</v>
+        <v>-2.980433820707781</v>
       </c>
       <c r="G30">
-        <v>-13.40853822110146</v>
+        <v>-14.72006877103068</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.27106714222493</v>
       </c>
       <c r="E31">
-        <v>-40.33458343885756</v>
+        <v>-41.27766305756196</v>
       </c>
       <c r="F31">
-        <v>-1.11564148530769</v>
+        <v>-2.969150707913233</v>
       </c>
       <c r="G31">
-        <v>-13.68101598225671</v>
+        <v>-14.87716243323294</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.16359510198873</v>
       </c>
       <c r="E32">
-        <v>-40.47849381434732</v>
+        <v>-41.08938495798206</v>
       </c>
       <c r="F32">
-        <v>-0.9679902072523976</v>
+        <v>-2.822840828768317</v>
       </c>
       <c r="G32">
-        <v>-13.38989653916982</v>
+        <v>-15.70615945226738</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.04448424873873</v>
       </c>
       <c r="E33">
-        <v>-40.46861494829959</v>
+        <v>-40.31642652232381</v>
       </c>
       <c r="F33">
-        <v>-1.192910496921981</v>
+        <v>-2.654952956525539</v>
       </c>
       <c r="G33">
-        <v>-13.25623657356729</v>
+        <v>-15.88356827717138</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.91913968256613</v>
       </c>
       <c r="E34">
-        <v>-40.29477135961913</v>
+        <v>-40.18386676693428</v>
       </c>
       <c r="F34">
-        <v>-0.978603412444715</v>
+        <v>-2.93344605804965</v>
       </c>
       <c r="G34">
-        <v>-14.53558365503648</v>
+        <v>-16.10519605884343</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.7907196969332</v>
       </c>
       <c r="E35">
-        <v>-39.31442013559461</v>
+        <v>-38.57748797490439</v>
       </c>
       <c r="F35">
-        <v>-1.261082701757988</v>
+        <v>-2.945247834531505</v>
       </c>
       <c r="G35">
-        <v>-13.10849685778623</v>
+        <v>-14.85455637301803</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.65715127096991</v>
       </c>
       <c r="E36">
-        <v>-38.85904131785728</v>
+        <v>-40.17339467079155</v>
       </c>
       <c r="F36">
-        <v>-1.322803680547451</v>
+        <v>-3.100112893031625</v>
       </c>
       <c r="G36">
-        <v>-13.93625407751621</v>
+        <v>-15.1735059171808</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.51732178745285</v>
       </c>
       <c r="E37">
-        <v>-39.11177545222537</v>
+        <v>-40.04040244613428</v>
       </c>
       <c r="F37">
-        <v>-0.8622002358069579</v>
+        <v>-2.44480389192926</v>
       </c>
       <c r="G37">
-        <v>-13.57865888000076</v>
+        <v>-15.16550929443069</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.38458786248291</v>
       </c>
       <c r="E38">
-        <v>-38.92607631859283</v>
+        <v>-38.95397851119109</v>
       </c>
       <c r="F38">
-        <v>-0.9365290973892352</v>
+        <v>-2.651635884485651</v>
       </c>
       <c r="G38">
-        <v>-14.00514487491568</v>
+        <v>-16.07386836640531</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.26232031568649</v>
       </c>
       <c r="E39">
-        <v>-38.16534023428129</v>
+        <v>-39.60274128295197</v>
       </c>
       <c r="F39">
-        <v>-0.8061172500764585</v>
+        <v>-3.12369031484773</v>
       </c>
       <c r="G39">
-        <v>-14.2248227452651</v>
+        <v>-14.88203059044844</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.1524624404231</v>
       </c>
       <c r="E40">
-        <v>-36.46913463183525</v>
+        <v>-38.69505848132853</v>
       </c>
       <c r="F40">
-        <v>-0.9431505718216875</v>
+        <v>-2.857721159702913</v>
       </c>
       <c r="G40">
-        <v>-14.18446388459584</v>
+        <v>-15.31481489825183</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.04861461009982</v>
       </c>
       <c r="E41">
-        <v>-38.57361612962783</v>
+        <v>-38.1195935898558</v>
       </c>
       <c r="F41">
-        <v>-0.6739712447862756</v>
+        <v>-2.755123147530042</v>
       </c>
       <c r="G41">
-        <v>-14.02969588063491</v>
+        <v>-15.20089406042719</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.95230594300757</v>
       </c>
       <c r="E42">
-        <v>-36.70938376336418</v>
+        <v>-37.62550311206391</v>
       </c>
       <c r="F42">
-        <v>-0.7944247493027691</v>
+        <v>-2.358312960769365</v>
       </c>
       <c r="G42">
-        <v>-13.58531473180746</v>
+        <v>-16.09664326444273</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.87234052591459</v>
       </c>
       <c r="E43">
-        <v>-37.42601930355202</v>
+        <v>-37.35990358304004</v>
       </c>
       <c r="F43">
-        <v>-0.7782345237292315</v>
+        <v>-2.495830896524719</v>
       </c>
       <c r="G43">
-        <v>-13.57780972506993</v>
+        <v>-15.29334435515688</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.80912516947728</v>
       </c>
       <c r="E44">
-        <v>-36.95628295897338</v>
+        <v>-38.39391495981845</v>
       </c>
       <c r="F44">
-        <v>-0.8852621613475872</v>
+        <v>-2.535344359114933</v>
       </c>
       <c r="G44">
-        <v>-14.49628085839425</v>
+        <v>-15.85927218345867</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.76148109154982</v>
       </c>
       <c r="E45">
-        <v>-37.04186432500734</v>
+        <v>-36.63458242970548</v>
       </c>
       <c r="F45">
-        <v>-1.043502097153508</v>
+        <v>-2.993656973248743</v>
       </c>
       <c r="G45">
-        <v>-14.7236656787591</v>
+        <v>-16.14668050499604</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.71990294509534</v>
       </c>
       <c r="E46">
-        <v>-36.36790965234179</v>
+        <v>-37.13126545886676</v>
       </c>
       <c r="F46">
-        <v>-0.6583408592538459</v>
+        <v>-2.672149627208338</v>
       </c>
       <c r="G46">
-        <v>-14.2057374502312</v>
+        <v>-16.11394914124926</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.68817806898865</v>
       </c>
       <c r="E47">
-        <v>-34.92254528212862</v>
+        <v>-37.27403013043259</v>
       </c>
       <c r="F47">
-        <v>-0.4871485846185034</v>
+        <v>-2.753150641812362</v>
       </c>
       <c r="G47">
-        <v>-14.70438506153838</v>
+        <v>-16.57376570865357</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.67115002839556</v>
       </c>
       <c r="E48">
-        <v>-35.60993140870092</v>
+        <v>-36.12287618802375</v>
       </c>
       <c r="F48">
-        <v>-0.7906563210769809</v>
+        <v>-2.384381551990456</v>
       </c>
       <c r="G48">
-        <v>-13.66861302339383</v>
+        <v>-16.7455581930502</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.66851993256751</v>
       </c>
       <c r="E49">
-        <v>-34.82230071725782</v>
+        <v>-35.52067292177274</v>
       </c>
       <c r="F49">
-        <v>-0.7716241352381873</v>
+        <v>-2.249998562094715</v>
       </c>
       <c r="G49">
-        <v>-14.8336519332103</v>
+        <v>-16.48073275790897</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.67761468024756</v>
       </c>
       <c r="E50">
-        <v>-33.69491899915226</v>
+        <v>-33.90133363713289</v>
       </c>
       <c r="F50">
-        <v>-0.9341860044873426</v>
+        <v>-2.465828379809676</v>
       </c>
       <c r="G50">
-        <v>-14.2142141020845</v>
+        <v>-16.10774186836313</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.69048779786671</v>
       </c>
       <c r="E51">
-        <v>-34.0429141127457</v>
+        <v>-35.16648511997381</v>
       </c>
       <c r="F51">
-        <v>-0.7367651843334496</v>
+        <v>-2.705657676967206</v>
       </c>
       <c r="G51">
-        <v>-15.367727347606</v>
+        <v>-16.34504011734532</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.71388723154279</v>
       </c>
       <c r="E52">
-        <v>-33.62181131477243</v>
+        <v>-34.41888387452152</v>
       </c>
       <c r="F52">
-        <v>-0.5101131122453331</v>
+        <v>-2.289240419120431</v>
       </c>
       <c r="G52">
-        <v>-14.89201022997657</v>
+        <v>-17.30657482704448</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.75218273152422</v>
       </c>
       <c r="E53">
-        <v>-32.71947890518906</v>
+        <v>-34.65015530633025</v>
       </c>
       <c r="F53">
-        <v>-0.8206034080849831</v>
+        <v>-2.250314511424845</v>
       </c>
       <c r="G53">
-        <v>-15.37441630486809</v>
+        <v>-16.33299469740068</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.8058121169395</v>
       </c>
       <c r="E54">
-        <v>-33.08086471642317</v>
+        <v>-33.20192894054424</v>
       </c>
       <c r="F54">
-        <v>-0.342558610097755</v>
+        <v>-2.475429596922027</v>
       </c>
       <c r="G54">
-        <v>-14.92351669187382</v>
+        <v>-17.0719034959477</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.87102716544102</v>
       </c>
       <c r="E55">
-        <v>-33.23838768477999</v>
+        <v>-32.12393702420332</v>
       </c>
       <c r="F55">
-        <v>-0.4978678981071553</v>
+        <v>-2.915658665060393</v>
       </c>
       <c r="G55">
-        <v>-14.95864820113656</v>
+        <v>-16.76635835067344</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.94097540999778</v>
       </c>
       <c r="E56">
-        <v>-32.57960340004013</v>
+        <v>-33.29400413830519</v>
       </c>
       <c r="F56">
-        <v>-0.8252824672121489</v>
+        <v>-2.231492958472805</v>
       </c>
       <c r="G56">
-        <v>-14.87482022226391</v>
+        <v>-16.80558334949549</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.02247893134064</v>
       </c>
       <c r="E57">
-        <v>-31.81543246819378</v>
+        <v>-32.80762338751136</v>
       </c>
       <c r="F57">
-        <v>-0.6301667310181781</v>
+        <v>-2.813052734357944</v>
       </c>
       <c r="G57">
-        <v>-14.42740495844972</v>
+        <v>-16.72738164276683</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.11631569315674</v>
       </c>
       <c r="E58">
-        <v>-31.58983747855366</v>
+        <v>-32.20966103716852</v>
       </c>
       <c r="F58">
-        <v>-0.9142954500423808</v>
+        <v>-2.680755485152837</v>
       </c>
       <c r="G58">
-        <v>-15.65376510329011</v>
+        <v>-16.16211757884566</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.22004545061252</v>
       </c>
       <c r="E59">
-        <v>-31.54497388655967</v>
+        <v>-32.58264427033628</v>
       </c>
       <c r="F59">
-        <v>-0.7496969349859705</v>
+        <v>-3.137129643246149</v>
       </c>
       <c r="G59">
-        <v>-14.70873346310421</v>
+        <v>-16.12747603032273</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.32521959174713</v>
       </c>
       <c r="E60">
-        <v>-31.69732986607373</v>
+        <v>-30.560995354855</v>
       </c>
       <c r="F60">
-        <v>-1.012499470152866</v>
+        <v>-3.143899986034652</v>
       </c>
       <c r="G60">
-        <v>-15.39440206828867</v>
+        <v>-16.46346991819444</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.42478257116049</v>
       </c>
       <c r="E61">
-        <v>-30.94360159528906</v>
+        <v>-31.32553535733298</v>
       </c>
       <c r="F61">
-        <v>-0.8230763648719418</v>
+        <v>-3.116162168778688</v>
       </c>
       <c r="G61">
-        <v>-14.8946090082249</v>
+        <v>-16.27348267551397</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.52500514360745</v>
       </c>
       <c r="E62">
-        <v>-30.72180373110438</v>
+        <v>-30.33599133107289</v>
       </c>
       <c r="F62">
-        <v>-1.078330957645852</v>
+        <v>-2.978502491343903</v>
       </c>
       <c r="G62">
-        <v>-15.08327368796243</v>
+        <v>-16.40765080985679</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.62472144865453</v>
       </c>
       <c r="E63">
-        <v>-29.36588804372772</v>
+        <v>-31.34977175022204</v>
       </c>
       <c r="F63">
-        <v>-1.15060733636172</v>
+        <v>-2.872428244686642</v>
       </c>
       <c r="G63">
-        <v>-15.02118606164617</v>
+        <v>-16.89140758732833</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.72163052988799</v>
       </c>
       <c r="E64">
-        <v>-30.3656347219271</v>
+        <v>-30.74567558183582</v>
       </c>
       <c r="F64">
-        <v>-0.9879433180810191</v>
+        <v>-2.907332331209969</v>
       </c>
       <c r="G64">
-        <v>-15.08365605597221</v>
+        <v>-17.37422416986672</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.80611163498061</v>
       </c>
       <c r="E65">
-        <v>-29.21135386821597</v>
+        <v>-30.44225650213688</v>
       </c>
       <c r="F65">
-        <v>-0.9622041376903395</v>
+        <v>-2.826997264943388</v>
       </c>
       <c r="G65">
-        <v>-14.85485101157103</v>
+        <v>-16.86182786293494</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.87659642500947</v>
       </c>
       <c r="E66">
-        <v>-29.56264344664999</v>
+        <v>-30.52026173115601</v>
       </c>
       <c r="F66">
-        <v>-1.192718868506213</v>
+        <v>-2.910542503100565</v>
       </c>
       <c r="G66">
-        <v>-15.72411916181793</v>
+        <v>-16.81258349803828</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.94034691728895</v>
       </c>
       <c r="E67">
-        <v>-28.68430289235925</v>
+        <v>-31.13375448310815</v>
       </c>
       <c r="F67">
-        <v>-0.6694529318095268</v>
+        <v>-3.43189215563957</v>
       </c>
       <c r="G67">
-        <v>-16.1126828575805</v>
+        <v>-17.80691081657669</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.99764234725381</v>
       </c>
       <c r="E68">
-        <v>-29.18517475997763</v>
+        <v>-30.48845825820014</v>
       </c>
       <c r="F68">
-        <v>-1.099533612441756</v>
+        <v>-3.511784576102786</v>
       </c>
       <c r="G68">
-        <v>-16.29686174811231</v>
+        <v>-16.70113563773149</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.04783644679613</v>
       </c>
       <c r="E69">
-        <v>-28.44343788836527</v>
+        <v>-29.18619819510336</v>
       </c>
       <c r="F69">
-        <v>-0.8719717013052193</v>
+        <v>-3.806870956355914</v>
       </c>
       <c r="G69">
-        <v>-15.87273617216689</v>
+        <v>-17.26906469081177</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.08186404205209</v>
       </c>
       <c r="E70">
-        <v>-30.40647250052827</v>
+        <v>-30.7391160872357</v>
       </c>
       <c r="F70">
-        <v>-1.064305658058721</v>
+        <v>-3.283491784686274</v>
       </c>
       <c r="G70">
-        <v>-16.06265720393657</v>
+        <v>-18.28807709216375</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.10531847608633</v>
       </c>
       <c r="E71">
-        <v>-28.38830371732188</v>
+        <v>-30.1659675102179</v>
       </c>
       <c r="F71">
-        <v>-1.408593029986806</v>
+        <v>-3.394911038808143</v>
       </c>
       <c r="G71">
-        <v>-15.27031288984017</v>
+        <v>-15.98818813730343</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.12571125843825</v>
       </c>
       <c r="E72">
-        <v>-28.67409571194596</v>
+        <v>-29.66956524644509</v>
       </c>
       <c r="F72">
-        <v>-1.384461311100298</v>
+        <v>-4.076892023085382</v>
       </c>
       <c r="G72">
-        <v>-16.02047423267517</v>
+        <v>-16.97068687663003</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.14516331018139</v>
       </c>
       <c r="E73">
-        <v>-28.31912674838071</v>
+        <v>-30.53451736733215</v>
       </c>
       <c r="F73">
-        <v>-1.379673768117924</v>
+        <v>-3.247258177046935</v>
       </c>
       <c r="G73">
-        <v>-15.0427989581993</v>
+        <v>-16.74558302214174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.16298057289171</v>
       </c>
       <c r="E74">
-        <v>-30.34614416979809</v>
+        <v>-30.64922587818345</v>
       </c>
       <c r="F74">
-        <v>-1.588551908717064</v>
+        <v>-4.146854607458793</v>
       </c>
       <c r="G74">
-        <v>-14.97346123715203</v>
+        <v>-15.47600701583171</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.17161232817475</v>
       </c>
       <c r="E75">
-        <v>-28.21132189615411</v>
+        <v>-30.67993119619246</v>
       </c>
       <c r="F75">
-        <v>-1.390556203315866</v>
+        <v>-3.644611574936607</v>
       </c>
       <c r="G75">
-        <v>-15.53008146667016</v>
+        <v>-16.59413052953839</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.17789681733803</v>
       </c>
       <c r="E76">
-        <v>-29.04382750077621</v>
+        <v>-32.02816885588911</v>
       </c>
       <c r="F76">
-        <v>-2.016256238623176</v>
+        <v>-3.623877697091674</v>
       </c>
       <c r="G76">
-        <v>-15.71810721111861</v>
+        <v>-16.55979520647784</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.18561019218692</v>
       </c>
       <c r="E77">
-        <v>-28.63040499471996</v>
+        <v>-31.20777691923752</v>
       </c>
       <c r="F77">
-        <v>-2.117748824067071</v>
+        <v>-3.382440938429973</v>
       </c>
       <c r="G77">
-        <v>-14.90529048340736</v>
+        <v>-17.18715020726081</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.19340617170486</v>
       </c>
       <c r="E78">
-        <v>-28.65315604813449</v>
+        <v>-31.01829877404559</v>
       </c>
       <c r="F78">
-        <v>-1.821147629105825</v>
+        <v>-3.936757013304765</v>
       </c>
       <c r="G78">
-        <v>-15.16254966671859</v>
+        <v>-16.61275069292402</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.19519626573353</v>
       </c>
       <c r="E79">
-        <v>-28.37676516555034</v>
+        <v>-31.99127990662263</v>
       </c>
       <c r="F79">
-        <v>-1.98680010044896</v>
+        <v>-4.484180008182607</v>
       </c>
       <c r="G79">
-        <v>-15.86382418357517</v>
+        <v>-17.2621886877267</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.18095905106941</v>
       </c>
       <c r="E80">
-        <v>-30.16471765139179</v>
+        <v>-30.20684151661114</v>
       </c>
       <c r="F80">
-        <v>-2.324471540915297</v>
+        <v>-3.518772678454662</v>
       </c>
       <c r="G80">
-        <v>-14.83087935132116</v>
+        <v>-16.37031116671935</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.15494401988646</v>
       </c>
       <c r="E81">
-        <v>-30.31230288353877</v>
+        <v>-33.16466865640912</v>
       </c>
       <c r="F81">
-        <v>-1.984451464576363</v>
+        <v>-4.042112257476417</v>
       </c>
       <c r="G81">
-        <v>-14.97251773167334</v>
+        <v>-16.22351495641698</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.11599683437102</v>
       </c>
       <c r="E82">
-        <v>-31.44765698013483</v>
+        <v>-34.64057305533002</v>
       </c>
       <c r="F82">
-        <v>-2.654404994278797</v>
+        <v>-4.479746423472334</v>
       </c>
       <c r="G82">
-        <v>-15.09678236903542</v>
+        <v>-16.23884609280935</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.06002364157564</v>
       </c>
       <c r="E83">
-        <v>-31.60212096429947</v>
+        <v>-32.59035852580835</v>
       </c>
       <c r="F83">
-        <v>-2.103721940774023</v>
+        <v>-4.113566692822171</v>
       </c>
       <c r="G83">
-        <v>-14.87112068762377</v>
+        <v>-16.08687384455634</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.97872713542572</v>
       </c>
       <c r="E84">
-        <v>-30.62537893405906</v>
+        <v>-33.82755573859992</v>
       </c>
       <c r="F84">
-        <v>-2.347682334811978</v>
+        <v>-4.486951493534625</v>
       </c>
       <c r="G84">
-        <v>-15.68309488149528</v>
+        <v>-16.59944064458339</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.86413594604069</v>
       </c>
       <c r="E85">
-        <v>-31.97241654814368</v>
+        <v>-33.61757492733825</v>
       </c>
       <c r="F85">
-        <v>-1.988927809346353</v>
+        <v>-4.277564191483672</v>
       </c>
       <c r="G85">
-        <v>-15.44869004931441</v>
+        <v>-14.66148370189496</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.72350106331146</v>
       </c>
       <c r="E86">
-        <v>-33.01305761086932</v>
+        <v>-33.24469811330967</v>
       </c>
       <c r="F86">
-        <v>-2.653417553640521</v>
+        <v>-4.806669251890583</v>
       </c>
       <c r="G86">
-        <v>-15.08266785812874</v>
+        <v>-16.1096785375036</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.55745839590792</v>
       </c>
       <c r="E87">
-        <v>-34.44688116507394</v>
+        <v>-34.60506076216186</v>
       </c>
       <c r="F87">
-        <v>-2.363406950846376</v>
+        <v>-4.313153230815427</v>
       </c>
       <c r="G87">
-        <v>-15.13784472063177</v>
+        <v>-15.751459302154</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.36579866388534</v>
       </c>
       <c r="E88">
-        <v>-34.18737696206439</v>
+        <v>-36.19853113903289</v>
       </c>
       <c r="F88">
-        <v>-2.429625654435688</v>
+        <v>-4.423538324974515</v>
       </c>
       <c r="G88">
-        <v>-15.08179056356084</v>
+        <v>-15.50882776430804</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.14454993118537</v>
       </c>
       <c r="E89">
-        <v>-36.08177802216714</v>
+        <v>-37.70466083771799</v>
       </c>
       <c r="F89">
-        <v>-2.26060226505154</v>
+        <v>-4.461058693670148</v>
       </c>
       <c r="G89">
-        <v>-14.94715895284252</v>
+        <v>-14.35832049413621</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.89325399603872</v>
       </c>
       <c r="E90">
-        <v>-36.46248683199199</v>
+        <v>-37.59669069619011</v>
       </c>
       <c r="F90">
-        <v>-2.695156914894885</v>
+        <v>-4.776272392402596</v>
       </c>
       <c r="G90">
-        <v>-15.09372342495714</v>
+        <v>-16.28017659859438</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.62447117494157</v>
       </c>
       <c r="E91">
-        <v>-38.19348470023896</v>
+        <v>-39.25969352721191</v>
       </c>
       <c r="F91">
-        <v>-2.604437488940767</v>
+        <v>-5.038092238048962</v>
       </c>
       <c r="G91">
-        <v>-14.50144199888998</v>
+        <v>-15.97084418922319</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.34272155375197</v>
       </c>
       <c r="E92">
-        <v>-39.42203026343888</v>
+        <v>-41.01262732355204</v>
       </c>
       <c r="F92">
-        <v>-2.674135594426299</v>
+        <v>-4.127047989427349</v>
       </c>
       <c r="G92">
-        <v>-14.62214779979734</v>
+        <v>-14.6606312364186</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.05258589313297</v>
       </c>
       <c r="E93">
-        <v>-40.06643664320438</v>
+        <v>-42.45779923361988</v>
       </c>
       <c r="F93">
-        <v>-2.805118367721592</v>
+        <v>-5.020843305070953</v>
       </c>
       <c r="G93">
-        <v>-14.15574490204266</v>
+        <v>-15.87663268426661</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.75264413443089</v>
       </c>
       <c r="E94">
-        <v>-42.19883844749126</v>
+        <v>-42.13472657672766</v>
       </c>
       <c r="F94">
-        <v>-2.774287572812775</v>
+        <v>-4.318919504053542</v>
       </c>
       <c r="G94">
-        <v>-13.84771188179564</v>
+        <v>-15.54144325896094</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.451074440149352</v>
       </c>
       <c r="E95">
-        <v>-42.58098957628754</v>
+        <v>-43.72946945479485</v>
       </c>
       <c r="F95">
-        <v>-2.910866370960273</v>
+        <v>-5.310047009701181</v>
       </c>
       <c r="G95">
-        <v>-14.2774389007935</v>
+        <v>-15.93964229751556</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.160799997674841</v>
       </c>
       <c r="E96">
-        <v>-45.05213482177018</v>
+        <v>-44.44601442550253</v>
       </c>
       <c r="F96">
-        <v>-3.202537489406756</v>
+        <v>-4.944564901506769</v>
       </c>
       <c r="G96">
-        <v>-15.05353009156485</v>
+        <v>-16.85483930130154</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.887774959388139</v>
       </c>
       <c r="E97">
-        <v>-45.4280434491469</v>
+        <v>-45.97123390636696</v>
       </c>
       <c r="F97">
-        <v>-2.864689465730847</v>
+        <v>-5.031746328445795</v>
       </c>
       <c r="G97">
-        <v>-14.92637369267421</v>
+        <v>-15.49621624107619</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.636422898792308</v>
       </c>
       <c r="E98">
-        <v>-48.60015911110635</v>
+        <v>-47.2479080913204</v>
       </c>
       <c r="F98">
-        <v>-2.887697545270351</v>
+        <v>-5.124050252168311</v>
       </c>
       <c r="G98">
-        <v>-14.87142194726785</v>
+        <v>-15.29845418219675</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.404085192441617</v>
       </c>
       <c r="E99">
-        <v>-49.4610865507191</v>
+        <v>-49.98138783606738</v>
       </c>
       <c r="F99">
-        <v>-2.742113795287665</v>
+        <v>-4.705122820445564</v>
       </c>
       <c r="G99">
-        <v>-15.39793607565185</v>
+        <v>-16.22822917326491</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.198820426741056</v>
       </c>
       <c r="E100">
-        <v>-51.20809031034618</v>
+        <v>-50.97144131565334</v>
       </c>
       <c r="F100">
-        <v>-2.582401012980385</v>
+        <v>-5.174370923925483</v>
       </c>
       <c r="G100">
-        <v>-14.17885913099785</v>
+        <v>-16.24055433430761</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.024592363559734</v>
       </c>
       <c r="E101">
-        <v>-52.83970062742831</v>
+        <v>-53.74987408975597</v>
       </c>
       <c r="F101">
-        <v>-2.894322978967592</v>
+        <v>-4.513091351521911</v>
       </c>
       <c r="G101">
-        <v>-14.86953493631046</v>
+        <v>-16.50137897516463</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.883879283715252</v>
       </c>
       <c r="E102">
-        <v>-54.92790452540032</v>
+        <v>-54.98411760537604</v>
       </c>
       <c r="F102">
-        <v>-2.426442405545655</v>
+        <v>-5.262712415447569</v>
       </c>
       <c r="G102">
-        <v>-14.7105492973325</v>
+        <v>-17.3857001759786</v>
       </c>
     </row>
   </sheetData>
